--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3DC165-91CA-4918-829C-7AEE3A9D8E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3209DAA-A293-4168-A7E4-D6EA73A98DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S03aH03,S02aH02,S01aH03,S04aH02,S01aH05,S03aH02,S04aH05,S03aH05,S01aH04,S03aH04,S02aH04,S02aH05,S02aH03,S01aH02,S04aH04</t>
+    <t>S03aH02,S02aH02,S01aH04,S04aH03,S02aH03,S02aH04,S02aH05,S04aH02,S01aH05,S03aH04,S03aH03,S04aH05,S03aH05,S01aH03,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S03aH01,S01aH06,S02aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
+    <t>S03aH01,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S03aH01,S01aH06,S02aH06,S01aH01,S04aH01,S04aH06,S03aH06</v>
+        <v>S03aH01,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S03aH03,S02aH02,S01aH03,S04aH02,S01aH05,S03aH02,S04aH05,S03aH05,S01aH04,S03aH04,S02aH04,S02aH05,S02aH03,S01aH02,S04aH04</v>
+        <v>S03aH02,S02aH02,S01aH04,S04aH03,S02aH03,S02aH04,S02aH05,S04aH02,S01aH05,S03aH04,S03aH03,S04aH05,S03aH05,S01aH03,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8208D17-1039-4237-9972-A8DE63E0B007}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2219DC5D-917E-4BEF-B3B9-AB6ECF42E9F1}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749A05A9-9453-4A84-92A2-340943164192}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D16ED3-DDEE-4C22-9127-6197355053CC}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1727FB21-1E2D-4A11-808F-36CADFF9FE59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B09A3EC-1B86-4399-9003-3511563A07F5}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485662CD-9D02-4A90-BC26-DE5D36749B1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1560450A-53AE-4141-81AE-015D6EB0D86E}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80857,7 +80857,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>330</v>
@@ -81077,7 +81077,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>330</v>
@@ -81121,7 +81121,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>330</v>
@@ -81165,7 +81165,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>330</v>
@@ -81783,7 +81783,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>330</v>
@@ -81829,7 +81829,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>330</v>
@@ -81921,7 +81921,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>330</v>
@@ -81967,7 +81967,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>330</v>
@@ -82013,7 +82013,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>330</v>
@@ -82036,7 +82036,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>330</v>
@@ -82128,7 +82128,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>330</v>
@@ -82243,7 +82243,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>330</v>
@@ -82312,7 +82312,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>330</v>
@@ -82358,7 +82358,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>330</v>
@@ -82409,7 +82409,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>330</v>
@@ -82437,7 +82437,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>330</v>
@@ -82451,7 +82451,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>330</v>
@@ -82465,7 +82465,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>330</v>
@@ -82493,7 +82493,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>330</v>
@@ -82535,7 +82535,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>330</v>
@@ -82591,7 +82591,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>330</v>
@@ -82689,7 +82689,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>330</v>
@@ -82955,7 +82955,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>330</v>
@@ -82969,7 +82969,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>330</v>
@@ -82983,7 +82983,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>330</v>
@@ -82997,7 +82997,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>330</v>
@@ -83011,7 +83011,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>330</v>
@@ -83137,7 +83137,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>330</v>
@@ -83179,7 +83179,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>330</v>
@@ -83221,7 +83221,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>330</v>
@@ -83235,7 +83235,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>330</v>
@@ -83249,7 +83249,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>330</v>
@@ -83263,7 +83263,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>330</v>
@@ -83277,7 +83277,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>330</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3209DAA-A293-4168-A7E4-D6EA73A98DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89626AE0-5D17-41BB-811B-E3621FF8CF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S02aH02,S01aH04,S04aH03,S02aH03,S02aH04,S02aH05,S04aH02,S01aH05,S03aH04,S03aH03,S04aH05,S03aH05,S01aH03,S01aH02,S04aH04</t>
+    <t>S02aH04,S02aH05,S03aH04,S01aH05,S03aH05,S01aH03,S04aH02,S02aH02,S04aH03,S04aH05,S01aH04,S03aH03,S03aH02,S02aH03,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</t>
+    <t>S02aH06,S03aH01,S02aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</v>
+        <v>S02aH06,S03aH01,S02aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH02,S02aH02,S01aH04,S04aH03,S02aH03,S02aH04,S02aH05,S04aH02,S01aH05,S03aH04,S03aH03,S04aH05,S03aH05,S01aH03,S01aH02,S04aH04</v>
+        <v>S02aH04,S02aH05,S03aH04,S01aH05,S03aH05,S01aH03,S04aH02,S02aH02,S04aH03,S04aH05,S01aH04,S03aH03,S03aH02,S02aH03,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2219DC5D-917E-4BEF-B3B9-AB6ECF42E9F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8391FB04-32E2-4E65-BA1D-4FF9F61F1305}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D16ED3-DDEE-4C22-9127-6197355053CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72EFC319-5F12-43ED-966D-B63CD00F20A4}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B09A3EC-1B86-4399-9003-3511563A07F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAE8685-04D8-4B57-A7F4-9A6B4F810F43}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1560450A-53AE-4141-81AE-015D6EB0D86E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F13A3A-3EA2-48CC-9513-5F331ACADC46}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80769,7 +80769,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>330</v>
@@ -81077,7 +81077,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>330</v>
@@ -81121,7 +81121,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>330</v>
@@ -81165,7 +81165,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="S21" t="s">
         <v>330</v>
@@ -81783,7 +81783,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>330</v>
@@ -81967,7 +81967,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>330</v>
@@ -82036,7 +82036,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>330</v>
@@ -82128,7 +82128,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>330</v>
@@ -82151,7 +82151,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>330</v>
@@ -82243,7 +82243,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>330</v>
@@ -82312,7 +82312,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>330</v>
@@ -82358,7 +82358,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>330</v>
@@ -82451,7 +82451,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>330</v>
@@ -82465,7 +82465,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>330</v>
@@ -82535,7 +82535,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>330</v>
@@ -82591,7 +82591,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>330</v>
@@ -82689,7 +82689,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>330</v>
@@ -82801,7 +82801,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>330</v>
@@ -82955,7 +82955,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>330</v>
@@ -82969,7 +82969,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>330</v>
@@ -82983,7 +82983,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>330</v>
@@ -83011,7 +83011,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>330</v>
@@ -83025,7 +83025,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>330</v>
@@ -83137,7 +83137,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>330</v>
@@ -83179,7 +83179,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>330</v>
@@ -83235,7 +83235,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>330</v>
@@ -83263,7 +83263,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>330</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89626AE0-5D17-41BB-811B-E3621FF8CF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FE68A4-3677-40C3-8610-D1AD00037B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S03aH04,S01aH05,S03aH05,S01aH03,S04aH02,S02aH02,S04aH03,S04aH05,S01aH04,S03aH03,S03aH02,S02aH03,S01aH02,S04aH04</t>
+    <t>S02aH03,S04aH03,S03aH02,S02aH02,S04aH02,S02aH04,S02aH05,S03aH03,S01aH04,S03aH05,S04aH05,S01aH03,S01aH05,S03aH04,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH06,S03aH01,S02aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
+    <t>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S02aH06,S03aH06,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S03aH01,S02aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</v>
+        <v>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S02aH06,S03aH06,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S03aH04,S01aH05,S03aH05,S01aH03,S04aH02,S02aH02,S04aH03,S04aH05,S01aH04,S03aH03,S03aH02,S02aH03,S01aH02,S04aH04</v>
+        <v>S02aH03,S04aH03,S03aH02,S02aH02,S04aH02,S02aH04,S02aH05,S03aH03,S01aH04,S03aH05,S04aH05,S01aH03,S01aH05,S03aH04,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8391FB04-32E2-4E65-BA1D-4FF9F61F1305}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B5BA3B-DCAE-4953-8045-E77369F1981A}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72EFC319-5F12-43ED-966D-B63CD00F20A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0708222-050D-477B-AA2D-F64B58126078}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAE8685-04D8-4B57-A7F4-9A6B4F810F43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08D8FD1-A40B-4293-A187-97BEF79CE068}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F13A3A-3EA2-48CC-9513-5F331ACADC46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBB9963-899B-4846-ABE2-29D69336D15B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80857,7 +80857,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>330</v>
@@ -80901,7 +80901,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>330</v>
@@ -81829,7 +81829,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>330</v>
@@ -81921,7 +81921,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>330</v>
@@ -82013,7 +82013,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>330</v>
@@ -82036,7 +82036,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>330</v>
@@ -82312,7 +82312,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>330</v>
@@ -82437,7 +82437,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>330</v>
@@ -82451,7 +82451,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>330</v>
@@ -82493,7 +82493,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>330</v>
@@ -82619,7 +82619,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>330</v>
@@ -82675,7 +82675,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>330</v>
@@ -82787,7 +82787,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>330</v>
@@ -82997,7 +82997,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>330</v>
@@ -83067,7 +83067,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>330</v>
@@ -83179,7 +83179,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>330</v>
@@ -83221,7 +83221,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="S122" t="s">
         <v>330</v>
@@ -83277,7 +83277,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>330</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FE68A4-3677-40C3-8610-D1AD00037B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B9B24-934C-49EE-AE7D-B03B5765FBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH03,S04aH03,S03aH02,S02aH02,S04aH02,S02aH04,S02aH05,S03aH03,S01aH04,S03aH05,S04aH05,S01aH03,S01aH05,S03aH04,S01aH02,S04aH04</t>
+    <t>S02aH04,S02aH05,S03aH04,S01aH03,S01aH04,S01aH02,S04aH04,S03aH02,S04aH02,S01aH05,S03aH03,S03aH05,S02aH03,S02aH02,S04aH05,S04aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S02aH06,S03aH06,S01aH06</t>
+    <t>S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH01,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S02aH06,S03aH06,S01aH06</v>
+        <v>S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH01,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH03,S04aH03,S03aH02,S02aH02,S04aH02,S02aH04,S02aH05,S03aH03,S01aH04,S03aH05,S04aH05,S01aH03,S01aH05,S03aH04,S01aH02,S04aH04</v>
+        <v>S02aH04,S02aH05,S03aH04,S01aH03,S01aH04,S01aH02,S04aH04,S03aH02,S04aH02,S01aH05,S03aH03,S03aH05,S02aH03,S02aH02,S04aH05,S04aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B5BA3B-DCAE-4953-8045-E77369F1981A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C48CBBB-CF76-4C28-8773-D24169B99373}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0708222-050D-477B-AA2D-F64B58126078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34100492-551E-4102-A63A-AA336C772598}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08D8FD1-A40B-4293-A187-97BEF79CE068}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4EC6CFC-8C8E-403B-893E-7BB7A9C8A653}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBB9963-899B-4846-ABE2-29D69336D15B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAC54A3-FE87-41E3-AD7E-8FAFA7EAF610}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80769,7 +80769,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>330</v>
@@ -81341,7 +81341,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>330</v>
@@ -82151,7 +82151,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>330</v>
@@ -82266,7 +82266,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="S57" t="s">
         <v>330</v>
@@ -82358,7 +82358,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>330</v>
@@ -82409,7 +82409,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>330</v>
@@ -82423,7 +82423,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="S65" t="s">
         <v>330</v>
@@ -82535,7 +82535,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>330</v>
@@ -82591,7 +82591,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>330</v>
@@ -82801,7 +82801,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>330</v>
@@ -83025,7 +83025,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>330</v>
@@ -83249,7 +83249,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>330</v>
@@ -83263,7 +83263,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>330</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B9B24-934C-49EE-AE7D-B03B5765FBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE4F159-BE45-42E4-B473-28CABEEA6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S03aH04,S01aH03,S01aH04,S01aH02,S04aH04,S03aH02,S04aH02,S01aH05,S03aH03,S03aH05,S02aH03,S02aH02,S04aH05,S04aH03</t>
+    <t>S02aH04,S02aH05,S01aH04,S01aH05,S03aH03,S04aH03,S01aH03,S02aH03,S03aH04,S01aH02,S04aH04,S04aH05,S03aH02,S03aH05,S02aH02,S04aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH01,S01aH06</t>
+    <t>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S03aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH01,S01aH06</v>
+        <v>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S03aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S03aH04,S01aH03,S01aH04,S01aH02,S04aH04,S03aH02,S04aH02,S01aH05,S03aH03,S03aH05,S02aH03,S02aH02,S04aH05,S04aH03</v>
+        <v>S02aH04,S02aH05,S01aH04,S01aH05,S03aH03,S04aH03,S01aH03,S02aH03,S03aH04,S01aH02,S04aH04,S04aH05,S03aH02,S03aH05,S02aH02,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C48CBBB-CF76-4C28-8773-D24169B99373}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38CBB03-4698-4476-BA46-0837ACB302B2}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34100492-551E-4102-A63A-AA336C772598}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228B0193-8E8B-4CEB-9FEE-AC9F2BB747AB}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4EC6CFC-8C8E-403B-893E-7BB7A9C8A653}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D128C7B-6A13-4DEF-85C4-744BC0CA52CD}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAC54A3-FE87-41E3-AD7E-8FAFA7EAF610}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28CFE683-5BF8-4524-88FB-2BDC37DFE09A}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80769,7 +80769,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>330</v>
@@ -80901,7 +80901,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>330</v>
@@ -81341,7 +81341,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>330</v>
@@ -82036,7 +82036,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>330</v>
@@ -82151,7 +82151,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>330</v>
@@ -82266,7 +82266,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="S57" t="s">
         <v>330</v>
@@ -82312,7 +82312,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>330</v>
@@ -82358,7 +82358,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>330</v>
@@ -82409,7 +82409,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>330</v>
@@ -82423,7 +82423,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="S65" t="s">
         <v>330</v>
@@ -82451,7 +82451,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>330</v>
@@ -82535,7 +82535,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>330</v>
@@ -82591,7 +82591,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>330</v>
@@ -82619,7 +82619,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>330</v>
@@ -82675,7 +82675,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>330</v>
@@ -82787,7 +82787,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>330</v>
@@ -82801,7 +82801,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>330</v>
@@ -83025,7 +83025,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>330</v>
@@ -83067,7 +83067,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>330</v>
@@ -83179,7 +83179,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>330</v>
@@ -83249,7 +83249,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>330</v>
@@ -83263,7 +83263,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>330</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE4F159-BE45-42E4-B473-28CABEEA6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5F4A1B-6E83-4757-825B-68973B3E04B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,13 +999,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S01aH04,S01aH05,S03aH03,S04aH03,S01aH03,S02aH03,S03aH04,S01aH02,S04aH04,S04aH05,S03aH02,S03aH05,S02aH02,S04aH02</t>
+    <t>S03aH04,S01aH04,S03aH05,S02aH04,S02aH05,S01aH03,S02aH03,S04aH03,S03aH02,S01aH02,S04aH04,S04aH05,S02aH02,S03aH03,S04aH02,S01aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S03aH01</t>
+    <t>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S03aH06,S03aH01,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S03aH01</v>
+        <v>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S03aH06,S03aH01,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S01aH04,S01aH05,S03aH03,S04aH03,S01aH03,S02aH03,S03aH04,S01aH02,S04aH04,S04aH05,S03aH02,S03aH05,S02aH02,S04aH02</v>
+        <v>S03aH04,S01aH04,S03aH05,S02aH04,S02aH05,S01aH03,S02aH03,S04aH03,S03aH02,S01aH02,S04aH04,S04aH05,S02aH02,S03aH03,S04aH02,S01aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1733,7 +1733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38CBB03-4698-4476-BA46-0837ACB302B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1072D82B-1C5E-4B79-9760-45E18C50EB6E}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1835,7 +1835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228B0193-8E8B-4CEB-9FEE-AC9F2BB747AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049EF14C-0EF3-4CAD-BBE5-092972654796}">
   <dimension ref="B9:O1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36025,7 +36025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D128C7B-6A13-4DEF-85C4-744BC0CA52CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD12575-81BB-4768-8707-94CD72C488F6}">
   <dimension ref="B9:EQ120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80618,7 +80618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28CFE683-5BF8-4524-88FB-2BDC37DFE09A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91CEB471-E0B8-4D6C-9040-232E400222A5}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80769,7 +80769,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>330</v>
@@ -80857,7 +80857,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>330</v>
@@ -80901,7 +80901,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>330</v>
@@ -81121,7 +81121,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>330</v>
@@ -81341,7 +81341,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>330</v>
@@ -81783,7 +81783,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>330</v>
@@ -81967,7 +81967,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>330</v>
@@ -82036,7 +82036,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>330</v>
@@ -82105,7 +82105,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>330</v>
@@ -82151,7 +82151,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>330</v>
@@ -82197,7 +82197,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>330</v>
@@ -82243,7 +82243,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>330</v>
@@ -82266,7 +82266,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="S57" t="s">
         <v>330</v>
@@ -82312,7 +82312,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>330</v>
@@ -82358,7 +82358,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>330</v>
@@ -82423,7 +82423,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="S65" t="s">
         <v>330</v>
@@ -82451,7 +82451,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>330</v>
@@ -82465,7 +82465,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>330</v>
@@ -82535,7 +82535,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>330</v>
@@ -82591,7 +82591,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>330</v>
@@ -82619,7 +82619,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>330</v>
@@ -82675,7 +82675,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>330</v>
@@ -82689,7 +82689,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>330</v>
@@ -82787,7 +82787,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>330</v>
@@ -82801,7 +82801,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>330</v>
@@ -82829,7 +82829,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>330</v>
@@ -82969,7 +82969,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>330</v>
@@ -83025,7 +83025,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>330</v>
@@ -83067,7 +83067,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>330</v>
@@ -83137,7 +83137,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>330</v>
@@ -83179,7 +83179,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>330</v>
@@ -83221,7 +83221,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>330</v>
@@ -83263,7 +83263,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>330</v>
